--- a/output/pdf_financials_xlsx/LMG.xlsx
+++ b/output/pdf_financials_xlsx/LMG.xlsx
@@ -1279,16 +1279,16 @@
         <v>-2.63718</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.413693</v>
+        <v>-2.413693</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>5.648755</v>
+        <v>-5.648755</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>5.115924</v>
+        <v>-5.115924</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.522294</v>
+        <v>-0.522294</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.341467</v>
@@ -1579,16 +1579,16 @@
         <v>-2.63718</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.413693</v>
+        <v>-2.413693</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5.648755</v>
+        <v>-5.648755</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5.115924</v>
+        <v>-5.115924</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.522294</v>
+        <v>-0.522294</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.341467</v>
@@ -1753,16 +1753,16 @@
         <v>-2.63718</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.413693</v>
+        <v>-2.413693</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.648755</v>
+        <v>-5.648755</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5.115924</v>
+        <v>-5.115924</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.522294</v>
+        <v>-0.522294</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.341467</v>
@@ -1939,16 +1939,16 @@
         <v>87.90600000000001</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-120.68465</v>
+        <v>120.68465</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-15.690986</v>
+        <v>15.690986</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-17.05308</v>
+        <v>17.05308</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-26.1147</v>
+        <v>26.1147</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2005,16 +2005,16 @@
         <v>-2.63718</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.413693</v>
+        <v>-2.413693</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>5.648755</v>
+        <v>-5.648755</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.115924</v>
+        <v>-5.115924</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.522294</v>
+        <v>-0.522294</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.341467</v>
@@ -2121,16 +2121,16 @@
         <v>-2.629226</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.421371</v>
+        <v>-2.406015</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.659438</v>
+        <v>-5.638072</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.122634</v>
+        <v>-5.109214</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.52618</v>
+        <v>-0.518408</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.338397</v>
@@ -2271,16 +2271,16 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -5856,10 +5856,10 @@
         <v>1.836778</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.404549</v>
+        <v>0.166687</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.719143</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -6443,16 +6443,16 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.107225</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.135463</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.038017</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.057457</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>0</v>
@@ -6617,16 +6617,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.450982</v>
+        <v>0.558207</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.175715</v>
+        <v>-0.311178</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.129607</v>
+        <v>-0.09159</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.166123</v>
+        <v>0.108666</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-0.151223</v>
@@ -24673,7 +24673,11 @@
           <t>Reserves (Note 13) 995,937</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -44877,7 +44881,11 @@
           <t>Decrease (increase) in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E370" s="5" t="n">
         <v>0.107225</v>
       </c>
@@ -56302,13 +56310,13 @@
         </is>
       </c>
       <c r="K485" s="5" t="n">
-        <v>5.115924</v>
+        <v>-5.115924</v>
       </c>
       <c r="L485" s="5" t="n">
-        <v>0.522294</v>
+        <v>-0.522294</v>
       </c>
       <c r="M485" s="5" t="n">
-        <v>0.341467</v>
+        <v>-0.341467</v>
       </c>
       <c r="N485" t="inlineStr">
         <is>
@@ -56504,13 +56512,13 @@
         </is>
       </c>
       <c r="K487" s="5" t="n">
-        <v>5.211015</v>
+        <v>-5.211015</v>
       </c>
       <c r="L487" s="5" t="n">
-        <v>0.427203</v>
+        <v>-0.427203</v>
       </c>
       <c r="M487" s="5" t="n">
-        <v>0.341467</v>
+        <v>-0.341467</v>
       </c>
       <c r="N487" t="inlineStr">
         <is>
@@ -57986,10 +57994,10 @@
         </is>
       </c>
       <c r="J502" s="5" t="n">
-        <v>5.648755</v>
+        <v>-5.648755</v>
       </c>
       <c r="K502" s="5" t="n">
-        <v>5.115924</v>
+        <v>-5.115924</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -58190,10 +58198,10 @@
         </is>
       </c>
       <c r="J504" s="5" t="n">
-        <v>5.648755</v>
+        <v>-5.648755</v>
       </c>
       <c r="K504" s="5" t="n">
-        <v>5.211015</v>
+        <v>-5.211015</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -59189,10 +59197,10 @@
         </is>
       </c>
       <c r="I514" s="5" t="n">
-        <v>2.413693</v>
+        <v>-2.413693</v>
       </c>
       <c r="J514" s="5" t="n">
-        <v>5.648755</v>
+        <v>-5.648755</v>
       </c>
       <c r="K514" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LMG.xlsx
+++ b/output/pdf_financials_xlsx/LMG.xlsx
@@ -1035,40 +1035,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000674</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003849</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007482</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001604</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000362</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000258</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000231</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000217</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000122</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-6.1e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-4.4e-05</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1077,13 +1077,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000181</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.00034</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000241</v>
       </c>
     </row>
     <row r="13">
@@ -1993,40 +1993,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.68324</v>
+        <v>-2.683914</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.143815</v>
+        <v>-2.147664</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.404039</v>
+        <v>-4.411521</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.63718</v>
+        <v>-2.638784</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.413693</v>
+        <v>-2.414055</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.648755</v>
+        <v>-5.648497</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.115924</v>
+        <v>-5.115693</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.522294</v>
+        <v>-0.522077</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.341467</v>
+        <v>-0.341345</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.127815</v>
+        <v>2.127876</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.338287</v>
+        <v>-1.338243</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.707311</v>
+        <v>-0.7072310000000001</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-1.384725</v>
@@ -2035,13 +2035,13 @@
         <v>-1.052264</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.497503</v>
+        <v>-6.497684</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.511599</v>
+        <v>-1.511939</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.479457</v>
+        <v>-1.479698</v>
       </c>
     </row>
     <row r="28">
@@ -2109,40 +2109,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.68324</v>
+        <v>-2.683914</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.143815</v>
+        <v>-2.147664</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.392914</v>
+        <v>-4.400396</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.629226</v>
+        <v>-2.63083</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.406015</v>
+        <v>-2.406377</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.638072</v>
+        <v>-5.637814</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.109214</v>
+        <v>-5.108983</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.518408</v>
+        <v>-0.518191</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.338397</v>
+        <v>-0.338275</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.132409</v>
+        <v>2.13247</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.334937</v>
+        <v>-1.334893</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.654257</v>
+        <v>-0.654177</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.326739</v>
@@ -2151,13 +2151,13 @@
         <v>-0.98394</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.430225</v>
+        <v>-6.430406</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.452862</v>
+        <v>-1.453202</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.422023</v>
+        <v>-1.422264</v>
       </c>
     </row>
     <row r="30">
@@ -2416,55 +2416,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001553</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.761227</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.761227</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.047977</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.202131</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.043958</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.014929</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.047021</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.021899</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.070102</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.056244</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.047058</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.018279</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.020804</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.295219</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.07863299999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2532,55 +2532,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001553</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.761227</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.761227</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.047977</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.202131</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.043958</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.014929</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.047021</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.021899</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.070102</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.056244</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.047058</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.018279</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.020804</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.295219</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.07863299999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3228,55 +3228,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002228</v>
+        <v>0.000675</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.926581</v>
+        <v>0.165354</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.926581</v>
+        <v>0.165354</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.162886</v>
+        <v>0.114909</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.396077</v>
+        <v>0.193946</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.067192</v>
+        <v>0.023234</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.11681</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.017905</v>
+        <v>0.002976</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.14071</v>
+        <v>0.09368899999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.137791</v>
+        <v>0.115892</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.098662</v>
+        <v>0.02856</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.08572</v>
+        <v>0.029476</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.058176</v>
+        <v>0.011118</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.019656</v>
+        <v>0.001377</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.020804</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.30379</v>
+        <v>0.008571</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.108612</v>
+        <v>0.029979</v>
       </c>
     </row>
     <row r="49">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -50213,7 +50213,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -50314,7 +50314,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -50902,7 +50902,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -51508,7 +51508,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -52110,7 +52110,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -52928,7 +52928,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -53021,7 +53021,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -58864,7 +58864,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -58967,7 +58967,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -59882,7 +59882,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -60797,7 +60797,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -61906,7 +61906,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E541" s="5" t="n">
@@ -62811,7 +62811,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E550" s="5" t="n">

--- a/output/pdf_financials_xlsx/LMG.xlsx
+++ b/output/pdf_financials_xlsx/LMG.xlsx
@@ -4235,22 +4235,22 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.214038</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.569746</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.735228</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.974306</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>1.130779</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>1.343162</v>
       </c>
     </row>
     <row r="65">
@@ -4409,22 +4409,22 @@
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="68">
@@ -6907,22 +6907,22 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011804</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024522</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001154</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001343</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010096</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010018</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01032</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.043971</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -8275,22 +8275,22 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011804</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024522</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001154</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001343</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010096</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010018</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01032</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -8311,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.043971</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8333,22 +8333,22 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.125559</v>
+        <v>-1.137363</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.055629</v>
+        <v>-2.080151</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.921835</v>
+        <v>-3.922989</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.223523</v>
+        <v>-2.224866</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.546637</v>
+        <v>-2.556733</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-2.486753</v>
+        <v>-2.496771</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-1.017894</v>
@@ -8357,7 +8357,7 @@
         <v>-0.321179</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.255475</v>
+        <v>-0.265795</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.7284620000000001</v>
@@ -8369,7 +8369,7 @@
         <v>-1.083566</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.015809</v>
+        <v>-1.05978</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-0.22943</v>
@@ -29062,7 +29062,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -31280,7 +31284,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -33784,7 +33792,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -35172,7 +35184,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -36376,7 +36392,11 @@
           <t>Private placement 6,400,000 576,000 64,000</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -38889,7 +38909,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -45287,7 +45311,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -46600,7 +46628,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E387" s="5" t="n">
         <v>0.325918</v>
       </c>
@@ -47198,7 +47230,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E393" s="5" t="n">
         <v>-0.011804</v>
       </c>
